--- a/dataset/Task04/output4.xlsx
+++ b/dataset/Task04/output4.xlsx
@@ -591,7 +591,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
